--- a/public/templates/acm-template.xlsx
+++ b/public/templates/acm-template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
   <si>
     <t>纳管IP</t>
   </si>
@@ -90,10 +90,13 @@
     <t>系统模块</t>
   </si>
   <si>
+    <t>分组名称</t>
+  </si>
+  <si>
+    <t>端口</t>
+  </si>
+  <si>
     <t>path</t>
-  </si>
-  <si>
-    <t>端口</t>
   </si>
 </sst>
 </file>
@@ -601,7 +604,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1437,7 +1440,7 @@
         <v>19</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>21</v>

--- a/public/templates/acm-template.xlsx
+++ b/public/templates/acm-template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25068" windowHeight="13380"/>
+    <workbookView windowWidth="25068" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Linux服务器" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
   <si>
     <t>纳管IP</t>
   </si>
@@ -90,13 +90,10 @@
     <t>系统模块</t>
   </si>
   <si>
-    <t>分组名称</t>
+    <t>所属分组</t>
   </si>
   <si>
     <t>端口</t>
-  </si>
-  <si>
-    <t>path</t>
   </si>
 </sst>
 </file>
@@ -1440,7 +1437,7 @@
         <v>19</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>21</v>
